--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555600085</v>
+        <v>46157.93112909972</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112909972</v>
+        <v>46157.93136979375</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136979375</v>
+        <v>46157.93384351861</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384351861</v>
+        <v>46157.93696090542</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696090542</v>
+        <v>46158.28205125737</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205125737</v>
+        <v>46158.2965278815</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2965278815</v>
+        <v>46158.29807958943</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807958943</v>
+        <v>46158.33370711528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370711528</v>
+        <v>46158.37221946531</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Июль 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221946531</v>
+        <v>46158.37275797884</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
